--- a/_101_Items.xlsx
+++ b/_101_Items.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231BBC09-654B-4E18-BA3D-A0C6E0B26EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75573B0A-6993-4029-9D6D-8AA75D9FDDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,30 @@
   </si>
   <si>
     <t>9040008</t>
+  </si>
+  <si>
+    <t>grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGrade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -543,17 +567,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:D54"/>
+  <dimension ref="A2:E54"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="7" customWidth="1"/>
-    <col min="2" max="3" width="12.5703125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="10" width="30.5703125" customWidth="1"/>
-    <col min="11" max="37" width="12.5703125" customWidth="1"/>
+    <col min="2" max="4" width="12.5703125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="6" max="11" width="30.5703125" customWidth="1"/>
+    <col min="12" max="38" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -561,13 +585,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -575,13 +602,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E3" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>1010001</v>
       </c>
@@ -589,13 +619,16 @@
         <v>11</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6">
         <v>1010002</v>
       </c>
@@ -603,13 +636,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>1010003</v>
       </c>
@@ -617,13 +653,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6">
         <v>1010004</v>
       </c>
@@ -631,246 +670,296 @@
         <v>3</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
-    </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
-    </row>
-    <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-    </row>
-    <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-    </row>
-    <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-    </row>
-    <row r="22" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" s="9"/>
+    </row>
+    <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6"/>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
-    </row>
-    <row r="24" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" s="10"/>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
-    </row>
-    <row r="26" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
-    </row>
-    <row r="28" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28" s="9"/>
+    </row>
+    <row r="29" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D31" s="10"/>
+    </row>
+    <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-    </row>
-    <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D33" s="10"/>
+    </row>
+    <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D34" s="9"/>
+    </row>
+    <row r="35" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
-    </row>
-    <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D35" s="10"/>
+    </row>
+    <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
-    </row>
-    <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="6"/>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-    </row>
-    <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D37" s="10"/>
+    </row>
+    <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="5"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
-    </row>
-    <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" s="9"/>
+    </row>
+    <row r="39" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6"/>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
-    </row>
-    <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D39" s="10"/>
+    </row>
+    <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
-    </row>
-    <row r="41" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="6"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-    </row>
-    <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
-    </row>
-    <row r="43" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D42" s="9"/>
+    </row>
+    <row r="43" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="6"/>
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
-    </row>
-    <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="5"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
-    </row>
-    <row r="45" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D44" s="9"/>
+    </row>
+    <row r="45" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="6"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
-    </row>
-    <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D45" s="10"/>
+    </row>
+    <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="5"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
-    </row>
-    <row r="47" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="6"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
-    </row>
-    <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="5"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
-    </row>
-    <row r="49" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D48" s="9"/>
+    </row>
+    <row r="49" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="6"/>
       <c r="B49" s="10"/>
       <c r="C49" s="10"/>
-    </row>
-    <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D49" s="10"/>
+    </row>
+    <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="5"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
-    </row>
-    <row r="51" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="6"/>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
-    </row>
-    <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D51" s="10"/>
+    </row>
+    <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="5"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
-    </row>
-    <row r="53" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D52" s="9"/>
+    </row>
+    <row r="53" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="6"/>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
-    </row>
-    <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D53" s="10"/>
+    </row>
+    <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="5"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/_101_Items.xlsx
+++ b/_101_Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75573B0A-6993-4029-9D6D-8AA75D9FDDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE96AC4-5323-4C71-A718-1C9FAA187B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -196,42 +196,45 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,398 +571,399 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
   <dimension ref="A2:E54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="7" customWidth="1"/>
-    <col min="2" max="4" width="12.5703125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="11" width="30.5703125" customWidth="1"/>
-    <col min="12" max="38" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.5625" style="10" customWidth="1"/>
+    <col min="2" max="4" width="12.5625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="12.5625" style="12" customWidth="1"/>
+    <col min="6" max="11" width="30.5625" style="12" customWidth="1"/>
+    <col min="12" max="38" width="12.5625" style="12" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5">
+    <row r="4" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="4">
         <v>1010001</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6">
+    <row r="5" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="7">
         <v>1010002</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5">
+    <row r="6" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="4">
         <v>1010003</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6">
+    <row r="7" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="7">
         <v>1010004</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="6"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="6"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="6"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-    </row>
-    <row r="27" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="6"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-    </row>
-    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="5"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="6"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-    </row>
-    <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="5"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="6"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-    </row>
-    <row r="32" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="5"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="6"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-    </row>
-    <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="5"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="6"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-    </row>
-    <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-    </row>
-    <row r="37" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="6"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-    </row>
-    <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="5"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="6"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-    </row>
-    <row r="40" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="6"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="5"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="6"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-    </row>
-    <row r="44" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="5"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-    </row>
-    <row r="45" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="6"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-    </row>
-    <row r="46" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="5"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="6"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-    </row>
-    <row r="48" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="5"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="6"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-    </row>
-    <row r="50" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="5"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-    </row>
-    <row r="51" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="6"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-    </row>
-    <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="5"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-    </row>
-    <row r="53" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="6"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-    </row>
-    <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="5"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+    <row r="8" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="7"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A31" s="7"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="7"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="7"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A37" s="7"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="7"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A45" s="7"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A47" s="7"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A49" s="7"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A51" s="7"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
